--- a/data/trans_dic/P32E$casa_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P32E$casa_2023-Provincia-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, realiza el atracón de alcohol en casa</t>
+          <t>Población que, al menos, realiza el atracón de alcohol en casa (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -577,7 +577,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 36,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 61,41</t>
+          <t>0,0; 64,84</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 53,26</t>
+          <t>0,0; 50,48</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>21,28; 73,94</t>
+          <t>22,36; 73,73</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 77,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>21,51; 70,81</t>
+          <t>21,69; 72,98</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>15,12; 100,0</t>
+          <t>11,89; 100,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>9,9; 76,23</t>
+          <t>12,44; 76,88</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>25,12; 74,16</t>
+          <t>21,49; 72,87</t>
         </is>
       </c>
     </row>
@@ -777,12 +777,12 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>43,07; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>22,32; 100,0</t>
+          <t>23,32; 100,0</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>19,68; 54,9</t>
+          <t>18,64; 54,48</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 61,09</t>
+          <t>0,0; 60,47</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>19,05; 49,25</t>
+          <t>19,02; 48,02</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>41,02; 76,83</t>
+          <t>39,33; 75,9</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>8,89; 56,4</t>
+          <t>7,74; 55,47</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>34,24; 66,09</t>
+          <t>32,89; 64,53</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>47,93; 79,46</t>
+          <t>46,96; 78,41</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>28,13; 75,6</t>
+          <t>30,97; 77,16</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>48,74; 74,9</t>
+          <t>47,2; 74,39</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>43,15; 60,5</t>
+          <t>43,35; 61,03</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>21,41; 47,6</t>
+          <t>22,22; 47,09</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>39,39; 54,11</t>
+          <t>40,02; 55,19</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1029,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, realiza el atracón de alcohol en casa</t>
+          <t>Población que, al menos, realiza el atracón de alcohol en casa (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1139,7 +1139,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 985</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 6257</t>
+          <t>0; 6606</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 1073</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 6431</t>
+          <t>0; 6094</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>3192; 11091</t>
+          <t>3353; 11059</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 761</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3439; 11321</t>
+          <t>3468; 11667</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1665; 11007</t>
+          <t>1308; 11007</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1021; 7860</t>
+          <t>1282; 7927</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5355; 15808</t>
+          <t>4581; 15535</t>
         </is>
       </c>
     </row>
@@ -1431,12 +1431,12 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>235; 545</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>692; 3100</t>
+          <t>723; 3100</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>5404; 15072</t>
+          <t>5117; 14957</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 4303</t>
+          <t>0; 4259</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>6570; 16988</t>
+          <t>6561; 16566</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>13518; 25320</t>
+          <t>12960; 25011</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1359; 8624</t>
+          <t>1184; 8481</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>16519; 31886</t>
+          <t>15870; 31133</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>20188; 33472</t>
+          <t>19779; 33029</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>4483; 12048</t>
+          <t>4935; 12297</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>28297; 43485</t>
+          <t>27402; 43190</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>62190; 87186</t>
+          <t>62476; 87956</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>11715; 26045</t>
+          <t>12155; 25764</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>78322; 107576</t>
+          <t>79562; 109730</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P32E$casa_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P32E$casa_2023-Provincia-trans_dic.xlsx
@@ -549,7 +549,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>50,25%</t>
+          <t>54,86%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -559,7 +559,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>25,63%</t>
+          <t>22,85%</t>
         </is>
       </c>
     </row>
@@ -582,7 +582,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 76,53</t>
+          <t>0,0; 55,28</t>
         </is>
       </c>
     </row>
@@ -599,7 +599,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>21,29%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>18,03%</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 64,84</t>
+          <t>0,0; 62,61</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -632,7 +632,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 50,48</t>
+          <t>0,0; 55,12</t>
         </is>
       </c>
     </row>
@@ -649,7 +649,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>46,56%</t>
+          <t>52,87%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -659,7 +659,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>43,68%</t>
+          <t>49,96%</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>22,36; 73,73</t>
+          <t>28,99; 76,73</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -682,7 +682,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>21,69; 72,98</t>
+          <t>27,2; 73,36</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>59,82%</t>
+          <t>56,98%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>35,87%</t>
+          <t>34,87%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>48,23%</t>
+          <t>46,05%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>11,89; 100,0</t>
+          <t>13,47; 100,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>12,44; 76,88</t>
+          <t>9,58; 76,72</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>21,49; 72,87</t>
+          <t>21,24; 74,76</t>
         </is>
       </c>
     </row>
@@ -749,7 +749,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>76,64%</t>
+          <t>76,53%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>80,74%</t>
+          <t>82,04%</t>
         </is>
       </c>
     </row>
@@ -782,7 +782,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>23,32; 100,0</t>
+          <t>29,57; 100,0</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>34,72%</t>
+          <t>34,37%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>20,25%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>31,92%</t>
+          <t>31,44%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>18,64; 54,48</t>
+          <t>19,38; 54,71</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 60,47</t>
+          <t>0,0; 62,71</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>19,02; 48,02</t>
+          <t>19,29; 46,53</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>59,22%</t>
+          <t>60,05%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>27,22%</t>
+          <t>31,18%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>49,08%</t>
+          <t>51,12%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>39,33; 75,9</t>
+          <t>41,02; 75,54</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>7,74; 55,47</t>
+          <t>12,02; 57,63</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>32,89; 64,53</t>
+          <t>37,05; 65,82</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>64,18%</t>
+          <t>64,78%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>54,63%</t>
+          <t>55,48%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>61,56%</t>
+          <t>62,15%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>46,96; 78,41</t>
+          <t>47,95; 80,42</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>30,97; 77,16</t>
+          <t>30,16; 77,29</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>47,2; 74,39</t>
+          <t>48,68; 74,67</t>
         </is>
       </c>
     </row>
@@ -949,17 +949,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>52,14%</t>
+          <t>53,93%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>33,98%</t>
+          <t>35,37%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>47,15%</t>
+          <t>48,65%</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>43,35; 61,03</t>
+          <t>44,88; 62,33</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>22,22; 47,09</t>
+          <t>24,41; 49,8</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>40,02; 55,19</t>
+          <t>41,18; 56,08</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1421</t>
+          <t>1471</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1422</t>
+          <t>1471</t>
         </is>
       </c>
     </row>
@@ -1134,7 +1134,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 2829</t>
+          <t>0; 2681</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 4245</t>
+          <t>0; 3559</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>2116</t>
+          <t>2128</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -1194,7 +1194,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2116</t>
+          <t>2128</t>
         </is>
       </c>
     </row>
@@ -1207,7 +1207,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 6606</t>
+          <t>0; 6257</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -1217,7 +1217,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 6094</t>
+          <t>0; 6502</t>
         </is>
       </c>
     </row>
@@ -1257,7 +1257,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6984</t>
+          <t>8583</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1267,7 +1267,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6984</t>
+          <t>8583</t>
         </is>
       </c>
     </row>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>3353; 11059</t>
+          <t>4706; 12457</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3468; 11667</t>
+          <t>4672; 12603</t>
         </is>
       </c>
     </row>
@@ -1330,17 +1330,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>6584</t>
+          <t>6749</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3698</t>
+          <t>4037</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>10282</t>
+          <t>10786</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1308; 11007</t>
+          <t>1596; 11845</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1282; 7927</t>
+          <t>1109; 8883</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4581; 15535</t>
+          <t>4975; 17511</t>
         </is>
       </c>
     </row>
@@ -1403,17 +1403,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1959</t>
+          <t>2115</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>545</t>
+          <t>849</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2503</t>
+          <t>2964</t>
         </is>
       </c>
     </row>
@@ -1426,7 +1426,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 2556</t>
+          <t>0; 2764</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>723; 3100</t>
+          <t>1068; 3613</t>
         </is>
       </c>
     </row>
@@ -1476,17 +1476,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>9531</t>
+          <t>9379</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>1480</t>
+          <t>1445</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>11011</t>
+          <t>10824</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>5117; 14957</t>
+          <t>5288; 14929</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 4259</t>
+          <t>0; 4476</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>6561; 16566</t>
+          <t>6640; 16017</t>
         </is>
       </c>
     </row>
@@ -1549,17 +1549,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>19514</t>
+          <t>26368</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>4163</t>
+          <t>6125</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>23677</t>
+          <t>32494</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>12960; 25011</t>
+          <t>18015; 33173</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1184; 8481</t>
+          <t>2362; 11323</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>15870; 31133</t>
+          <t>23551; 41832</t>
         </is>
       </c>
     </row>
@@ -1622,17 +1622,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>27035</t>
+          <t>30293</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>8706</t>
+          <t>10249</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>35742</t>
+          <t>40541</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>19779; 33029</t>
+          <t>22421; 37609</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>4935; 12297</t>
+          <t>5571; 14277</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>27402; 43190</t>
+          <t>31758; 48709</t>
         </is>
       </c>
     </row>
@@ -1695,17 +1695,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>75145</t>
+          <t>87085</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>18592</t>
+          <t>22705</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>93737</t>
+          <t>109790</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>62476; 87956</t>
+          <t>72468; 100652</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>12155; 25764</t>
+          <t>15670; 31963</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>79562; 109730</t>
+          <t>92920; 126553</t>
         </is>
       </c>
     </row>
